--- a/data/input/master-input_companies.xlsx
+++ b/data/input/master-input_companies.xlsx
@@ -8,23 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alirizabagci/Documents/04_Projekte_Code/Python Projects/Upwork/singapore_ats_scraping/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38748E2A-F126-4E40-97D2-A412F68E6DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF5BDF42-A343-8C45-A4B5-279E676E14AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$221</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$113</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="643">
   <si>
     <t>Company</t>
   </si>
@@ -92,12 +92,6 @@
     <t>Baxter</t>
   </si>
   <si>
-    <t>BP</t>
-  </si>
-  <si>
-    <t>https://bpinternational.wd3.myworkdayjobs.com/en-US/bpCareers/details/Trading-Operator_RQ114403?locationCountry=80938777cac5440fab50d729f9634969</t>
-  </si>
-  <si>
     <t>Trading</t>
   </si>
   <si>
@@ -542,24 +536,15 @@
     <t>https://jobs.neste.com/search</t>
   </si>
   <si>
-    <t>NIPPON PAINT (SINGAPORE) COMPANY PRIVATE LIMITED</t>
-  </si>
-  <si>
     <t>https://www.nipponpaint.com</t>
   </si>
   <si>
-    <t>https://sg.jobstreet.com/Nippon-Paint-jobs/at-this-company</t>
-  </si>
-  <si>
     <t>PPG INDUSTRIES (SINGAPORE) PTE. LTD.</t>
   </si>
   <si>
     <t>https://www.ppg.com</t>
   </si>
   <si>
-    <t>https://careers.ppg.com/</t>
-  </si>
-  <si>
     <t>PRIME EVOLUE SINGAPORE PTE. LTD.</t>
   </si>
   <si>
@@ -788,9 +773,6 @@
     <t>Johnson Controls</t>
   </si>
   <si>
-    <t>https://www.johnsoncontrols.com/</t>
-  </si>
-  <si>
     <t>https://jobs.johnsoncontrols.com/job-search?production_JCI_jobs%5BrefinementList%5D%5Blocations_list%5D%5B0%5D=Singapore</t>
   </si>
   <si>
@@ -1103,15 +1085,6 @@
     <t xml:space="preserve">   aem_workday_json</t>
   </si>
   <si>
-    <t>Bumi Armada</t>
-  </si>
-  <si>
-    <t>https://www.bumiarmada.com/</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/company/bumi-armada/jobs/</t>
-  </si>
-  <si>
     <t>MacGregor</t>
   </si>
   <si>
@@ -1859,9 +1832,6 @@
     <t>UTAC</t>
   </si>
   <si>
-    <t>https://sg.jobstreet.com/UTAC-Group-jobs/at-this-company?source=COMPANY_JOBS</t>
-  </si>
-  <si>
     <t>VIS</t>
   </si>
   <si>
@@ -1962,6 +1932,27 @@
   </si>
   <si>
     <t>https://jobs.baxter.com/en/location/singapore-jobs/152/1880251/2</t>
+  </si>
+  <si>
+    <t>NIPPON PAINT (SINGAPORE)</t>
+  </si>
+  <si>
+    <t>https://sg.jobstreet.com/companies/nippon-paint-168554607347534/jobs</t>
+  </si>
+  <si>
+    <t>https://sg.jobstreet.com/companies/utac-group-168550975757665/jobs</t>
+  </si>
+  <si>
+    <t>https://bpinternational.wd3.myworkdayjobs.com/en-US/bpCareers?locationCountry=80938777cac5440fab50d729f9634969</t>
+  </si>
+  <si>
+    <t>https://jobs.johnsoncontrols.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BP </t>
+  </si>
+  <si>
+    <t>careers.ppg.com/us/en/search-results?m=3&amp;location=Singapore%2C%20North%20East</t>
   </si>
 </sst>
 </file>
@@ -2365,7 +2356,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G221"/>
+  <dimension ref="A1:G220"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="50.83203125" bestFit="1" customWidth="1"/>
@@ -2448,7 +2439,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -2465,12 +2456,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -2482,44 +2473,44 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>641</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C7" t="s">
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>23</v>
       </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="6" t="s">
+      <c r="C8" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="D8" t="s">
         <v>25</v>
       </c>
-      <c r="C8" t="s">
+      <c r="F8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D8" t="s">
+      <c r="G8" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
@@ -2533,121 +2524,121 @@
     </row>
     <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
         <v>9</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G10" s="6"/>
     </row>
     <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
         <v>9</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G11" s="6"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
         <v>9</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G12" s="6"/>
     </row>
     <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
         <v>9</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G13" s="6"/>
     </row>
     <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>41</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C15" t="s">
         <v>42</v>
       </c>
-      <c r="D14" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G14" s="6"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="D15" t="s">
         <v>43</v>
       </c>
-      <c r="C15" t="s">
+      <c r="F15" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="D15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>46</v>
       </c>
       <c r="G15" s="6"/>
     </row>
     <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="s">
         <v>47</v>
       </c>
-      <c r="C16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" t="s">
-        <v>49</v>
-      </c>
       <c r="F16" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G16" s="6"/>
     </row>
     <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
         <v>9</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>13</v>
@@ -2655,25 +2646,25 @@
     </row>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" t="s">
         <v>53</v>
       </c>
-      <c r="C18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" t="s">
-        <v>55</v>
-      </c>
       <c r="F18" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
         <v>9</v>
@@ -2687,10 +2678,10 @@
     </row>
     <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
         <v>9</v>
@@ -2704,27 +2695,27 @@
     </row>
     <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" t="s">
         <v>60</v>
       </c>
-      <c r="C21" t="s">
+      <c r="F21" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="D21" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D22" t="s">
         <v>9</v>
@@ -2733,32 +2724,32 @@
         <v>13</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
         <v>9</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D24" t="s">
         <v>9</v>
@@ -2772,52 +2763,52 @@
     </row>
     <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" t="s">
         <v>71</v>
       </c>
-      <c r="C25" t="s">
+      <c r="F25" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="D25" t="s">
-        <v>73</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" t="s">
         <v>75</v>
       </c>
-      <c r="B26" t="s">
+      <c r="D26" t="s">
         <v>76</v>
-      </c>
-      <c r="C26" t="s">
-        <v>77</v>
-      </c>
-      <c r="D26" t="s">
-        <v>78</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
     </row>
     <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" t="s">
         <v>79</v>
-      </c>
-      <c r="B27" t="s">
-        <v>80</v>
-      </c>
-      <c r="C27" t="s">
-        <v>81</v>
       </c>
       <c r="D27" t="s">
         <v>9</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>14</v>
@@ -2825,59 +2816,59 @@
     </row>
     <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" t="s">
         <v>83</v>
       </c>
-      <c r="B28" t="s">
+      <c r="D28" t="s">
+        <v>76</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
         <v>84</v>
       </c>
-      <c r="C28" t="s">
+      <c r="B29" t="s">
         <v>85</v>
       </c>
-      <c r="D28" t="s">
-        <v>78</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="C29" t="s">
         <v>86</v>
       </c>
-      <c r="B29" t="s">
+      <c r="D29" t="s">
+        <v>60</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="C29" t="s">
-        <v>88</v>
-      </c>
-      <c r="D29" t="s">
-        <v>62</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" t="s">
         <v>90</v>
       </c>
-      <c r="B30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" t="s">
-        <v>92</v>
-      </c>
       <c r="D30" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>14</v>
@@ -2885,95 +2876,95 @@
     </row>
     <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" t="s">
         <v>93</v>
       </c>
-      <c r="B31" t="s">
+      <c r="D31" t="s">
         <v>94</v>
       </c>
-      <c r="C31" t="s">
+      <c r="F31" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="D31" t="s">
-        <v>96</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" t="s">
         <v>98</v>
       </c>
-      <c r="B32" t="s">
-        <v>99</v>
-      </c>
-      <c r="C32" t="s">
-        <v>100</v>
-      </c>
       <c r="D32" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
     </row>
     <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" t="s">
         <v>101</v>
       </c>
-      <c r="B33" t="s">
+      <c r="D33" t="s">
+        <v>60</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C33" t="s">
+    </row>
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
         <v>103</v>
       </c>
-      <c r="D33" t="s">
-        <v>62</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G33" s="6" t="s">
+      <c r="B34" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+      <c r="C34" t="s">
         <v>105</v>
       </c>
-      <c r="B34" t="s">
+      <c r="D34" t="s">
+        <v>76</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
         <v>106</v>
       </c>
-      <c r="C34" t="s">
+      <c r="B35" t="s">
         <v>107</v>
       </c>
-      <c r="D34" t="s">
-        <v>78</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+      <c r="C35" t="s">
         <v>108</v>
       </c>
-      <c r="B35" t="s">
+      <c r="D35" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="C35" t="s">
-        <v>110</v>
-      </c>
-      <c r="D35" t="s">
-        <v>78</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>111</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>14</v>
@@ -2981,19 +2972,19 @@
     </row>
     <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
+        <v>110</v>
+      </c>
+      <c r="B36" t="s">
+        <v>111</v>
+      </c>
+      <c r="C36" t="s">
         <v>112</v>
       </c>
-      <c r="B36" t="s">
+      <c r="D36" t="s">
         <v>113</v>
       </c>
-      <c r="C36" t="s">
-        <v>114</v>
-      </c>
-      <c r="D36" t="s">
-        <v>115</v>
-      </c>
       <c r="F36" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>14</v>
@@ -3001,73 +2992,73 @@
     </row>
     <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
+        <v>114</v>
+      </c>
+      <c r="B37" t="s">
+        <v>115</v>
+      </c>
+      <c r="C37" t="s">
         <v>116</v>
-      </c>
-      <c r="B37" t="s">
-        <v>117</v>
-      </c>
-      <c r="C37" t="s">
-        <v>118</v>
       </c>
       <c r="D37" t="s">
         <v>9</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G37" s="6"/>
     </row>
     <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B38" t="s">
+        <v>118</v>
+      </c>
+      <c r="C38" t="s">
         <v>119</v>
       </c>
-      <c r="B38" t="s">
-        <v>120</v>
-      </c>
-      <c r="C38" t="s">
-        <v>121</v>
-      </c>
       <c r="D38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F38" s="8"/>
       <c r="G38" s="8"/>
     </row>
     <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
+        <v>120</v>
+      </c>
+      <c r="B39" t="s">
+        <v>121</v>
+      </c>
+      <c r="C39" t="s">
         <v>122</v>
       </c>
-      <c r="B39" t="s">
+      <c r="D39" t="s">
         <v>123</v>
       </c>
-      <c r="C39" t="s">
-        <v>124</v>
-      </c>
-      <c r="D39" t="s">
-        <v>125</v>
-      </c>
       <c r="F39" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
+        <v>124</v>
+      </c>
+      <c r="B40" t="s">
+        <v>125</v>
+      </c>
+      <c r="C40" t="s">
         <v>126</v>
       </c>
-      <c r="B40" t="s">
-        <v>127</v>
-      </c>
-      <c r="C40" t="s">
-        <v>128</v>
-      </c>
       <c r="D40" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>14</v>
@@ -3075,49 +3066,49 @@
     </row>
     <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
+        <v>127</v>
+      </c>
+      <c r="B41" t="s">
+        <v>128</v>
+      </c>
+      <c r="C41" t="s">
         <v>129</v>
       </c>
-      <c r="B41" t="s">
+      <c r="D41" t="s">
+        <v>76</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="C41" t="s">
+      <c r="B42" t="s">
         <v>131</v>
       </c>
-      <c r="D41" t="s">
-        <v>78</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="7" t="s">
+      <c r="C42" t="s">
         <v>132</v>
       </c>
-      <c r="B42" t="s">
+      <c r="D42" t="s">
         <v>133</v>
-      </c>
-      <c r="C42" t="s">
-        <v>134</v>
-      </c>
-      <c r="D42" t="s">
-        <v>135</v>
       </c>
       <c r="F42" s="8"/>
       <c r="G42" s="8"/>
     </row>
     <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>134</v>
+      </c>
+      <c r="B43" t="s">
+        <v>135</v>
+      </c>
+      <c r="C43" t="s">
         <v>136</v>
-      </c>
-      <c r="B43" t="s">
-        <v>137</v>
-      </c>
-      <c r="C43" t="s">
-        <v>138</v>
       </c>
       <c r="D43" t="s">
         <v>9</v>
@@ -3126,38 +3117,38 @@
         <v>14</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
+        <v>137</v>
+      </c>
+      <c r="B44" t="s">
+        <v>138</v>
+      </c>
+      <c r="C44" t="s">
         <v>139</v>
       </c>
-      <c r="B44" t="s">
+      <c r="D44" t="s">
+        <v>60</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="C44" t="s">
-        <v>141</v>
-      </c>
-      <c r="D44" t="s">
-        <v>62</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
+        <v>141</v>
+      </c>
+      <c r="B45" t="s">
+        <v>142</v>
+      </c>
+      <c r="C45" t="s">
         <v>143</v>
-      </c>
-      <c r="B45" t="s">
-        <v>144</v>
-      </c>
-      <c r="C45" t="s">
-        <v>145</v>
       </c>
       <c r="D45" t="s">
         <v>9</v>
@@ -3166,40 +3157,40 @@
         <v>14</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B46" t="s">
+        <v>145</v>
+      </c>
+      <c r="C46" t="s">
         <v>146</v>
       </c>
-      <c r="B46" t="s">
-        <v>147</v>
-      </c>
-      <c r="C46" t="s">
-        <v>148</v>
-      </c>
       <c r="D46" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
     </row>
     <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>147</v>
+      </c>
+      <c r="B47" t="s">
+        <v>148</v>
+      </c>
+      <c r="C47" t="s">
         <v>149</v>
       </c>
-      <c r="B47" t="s">
+      <c r="D47" t="s">
         <v>150</v>
       </c>
-      <c r="C47" t="s">
-        <v>151</v>
-      </c>
-      <c r="D47" t="s">
-        <v>152</v>
-      </c>
       <c r="F47" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>14</v>
@@ -3207,53 +3198,53 @@
     </row>
     <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>151</v>
+      </c>
+      <c r="B48" t="s">
+        <v>152</v>
+      </c>
+      <c r="C48" t="s">
         <v>153</v>
       </c>
-      <c r="B48" t="s">
-        <v>154</v>
-      </c>
-      <c r="C48" t="s">
-        <v>155</v>
-      </c>
       <c r="D48" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>154</v>
+      </c>
+      <c r="B49" t="s">
+        <v>155</v>
+      </c>
+      <c r="C49" t="s">
         <v>156</v>
       </c>
-      <c r="B49" t="s">
+      <c r="D49" t="s">
+        <v>60</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
         <v>157</v>
       </c>
-      <c r="C49" t="s">
+      <c r="B50" t="s">
         <v>158</v>
       </c>
-      <c r="D49" t="s">
-        <v>62</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="G49" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
+      <c r="C50" t="s">
         <v>159</v>
-      </c>
-      <c r="B50" t="s">
-        <v>160</v>
-      </c>
-      <c r="C50" t="s">
-        <v>161</v>
       </c>
       <c r="D50" t="s">
         <v>9</v>
@@ -3262,40 +3253,40 @@
         <v>14</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B51" t="s">
+        <v>161</v>
+      </c>
+      <c r="C51" t="s">
         <v>162</v>
       </c>
-      <c r="B51" t="s">
-        <v>163</v>
-      </c>
-      <c r="C51" t="s">
-        <v>164</v>
-      </c>
       <c r="D51" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F51" s="8"/>
       <c r="G51" s="8"/>
     </row>
     <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>163</v>
+      </c>
+      <c r="B52" t="s">
+        <v>164</v>
+      </c>
+      <c r="C52" t="s">
         <v>165</v>
       </c>
-      <c r="B52" t="s">
+      <c r="D52" t="s">
         <v>166</v>
       </c>
-      <c r="C52" t="s">
-        <v>167</v>
-      </c>
-      <c r="D52" t="s">
-        <v>168</v>
-      </c>
       <c r="F52" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>14</v>
@@ -3303,19 +3294,19 @@
     </row>
     <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>167</v>
+      </c>
+      <c r="B53" t="s">
+        <v>168</v>
+      </c>
+      <c r="C53" t="s">
         <v>169</v>
       </c>
-      <c r="B53" t="s">
-        <v>170</v>
-      </c>
-      <c r="C53" t="s">
-        <v>171</v>
-      </c>
       <c r="D53" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>14</v>
@@ -3323,59 +3314,59 @@
     </row>
     <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
+        <v>636</v>
+      </c>
+      <c r="B54" t="s">
+        <v>170</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="D54" t="s">
+        <v>166</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>171</v>
+      </c>
+      <c r="B55" t="s">
         <v>172</v>
       </c>
-      <c r="B54" t="s">
-        <v>173</v>
-      </c>
-      <c r="C54" t="s">
-        <v>174</v>
-      </c>
-      <c r="D54" t="s">
-        <v>168</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>175</v>
-      </c>
-      <c r="B55" t="s">
-        <v>176</v>
-      </c>
-      <c r="C55" t="s">
-        <v>177</v>
+      <c r="C55" s="2" t="s">
+        <v>642</v>
       </c>
       <c r="D55" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B56" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C56" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D56" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>14</v>
@@ -3383,19 +3374,19 @@
     </row>
     <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B57" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C57" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D57" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>14</v>
@@ -3403,19 +3394,19 @@
     </row>
     <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B58" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C58" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D58" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>14</v>
@@ -3423,19 +3414,19 @@
     </row>
     <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B59" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C59" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D59" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>14</v>
@@ -3443,13 +3434,13 @@
     </row>
     <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="7" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B60" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C60" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D60" t="s">
         <v>9</v>
@@ -3459,19 +3450,19 @@
     </row>
     <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B61" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C61" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D61" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>14</v>
@@ -3479,16 +3470,16 @@
     </row>
     <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B62" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C62" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D62" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>20</v>
@@ -3499,2792 +3490,2747 @@
     </row>
     <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
+        <v>197</v>
+      </c>
+      <c r="B63" t="s">
+        <v>198</v>
+      </c>
+      <c r="C63" t="s">
+        <v>199</v>
+      </c>
+      <c r="D63" t="s">
+        <v>76</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>200</v>
+      </c>
+      <c r="B64" t="s">
+        <v>201</v>
+      </c>
+      <c r="C64" t="s">
         <v>202</v>
       </c>
-      <c r="B63" t="s">
+      <c r="D64" t="s">
         <v>203</v>
       </c>
-      <c r="C63" t="s">
-        <v>204</v>
-      </c>
-      <c r="D63" t="s">
-        <v>78</v>
-      </c>
-      <c r="F63" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G63" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>205</v>
-      </c>
-      <c r="B64" t="s">
-        <v>206</v>
-      </c>
-      <c r="C64" t="s">
-        <v>207</v>
-      </c>
-      <c r="D64" t="s">
-        <v>208</v>
-      </c>
       <c r="F64" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B65" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C65" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D65" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F65" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B66" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C66" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D66" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F66" s="8"/>
       <c r="G66" s="8"/>
     </row>
     <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B67" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C67" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D67" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F67" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B68" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C68" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D68" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="7" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B69" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C69" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D69" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F69" s="8"/>
       <c r="G69" s="8"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="7" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B70" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C70" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D70" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F70" s="8"/>
       <c r="G70" s="8"/>
     </row>
     <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="7" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B71" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C71" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D71" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F71" s="8"/>
       <c r="G71" s="8"/>
     </row>
     <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B72" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C72" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D72" t="s">
         <v>9</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B73" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C73" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="D73" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B74" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C74" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D74" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B75" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C75" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D75" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B76" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C76" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D76" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B77" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C77" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D77" t="s">
         <v>9</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B78" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C78" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D78" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>253</v>
-      </c>
-      <c r="B79" t="s">
-        <v>254</v>
-      </c>
-      <c r="C79" t="s">
-        <v>255</v>
+        <v>248</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>249</v>
       </c>
       <c r="D79" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B80" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C80" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D80" t="s">
         <v>9</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B81" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C81" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="D81" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="G81" s="6"/>
     </row>
     <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
+        <v>260</v>
+      </c>
+      <c r="B82" t="s">
+        <v>261</v>
+      </c>
+      <c r="D82" t="s">
+        <v>262</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="G82" s="6"/>
+    </row>
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>263</v>
+      </c>
+      <c r="B83" t="s">
+        <v>264</v>
+      </c>
+      <c r="C83" t="s">
+        <v>265</v>
+      </c>
+      <c r="D83" t="s">
+        <v>71</v>
+      </c>
+      <c r="F83" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="G83" s="6"/>
+    </row>
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
         <v>266</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B84" t="s">
         <v>267</v>
       </c>
-      <c r="D82" t="s">
+      <c r="C84" t="s">
         <v>268</v>
       </c>
-      <c r="F82" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="G82" s="6"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
-        <v>269</v>
-      </c>
-      <c r="B83" t="s">
-        <v>270</v>
-      </c>
-      <c r="C83" t="s">
-        <v>271</v>
-      </c>
-      <c r="D83" t="s">
-        <v>73</v>
-      </c>
-      <c r="F83" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="G83" s="6"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>272</v>
-      </c>
-      <c r="B84" t="s">
-        <v>273</v>
-      </c>
-      <c r="C84" t="s">
-        <v>274</v>
-      </c>
       <c r="D84" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="G84" s="6"/>
     </row>
     <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B85" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C85" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="D85" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="G85" s="6"/>
     </row>
     <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
+        <v>272</v>
+      </c>
+      <c r="B86" t="s">
+        <v>273</v>
+      </c>
+      <c r="C86" t="s">
+        <v>274</v>
+      </c>
+      <c r="D86" t="s">
+        <v>275</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>276</v>
+      </c>
+      <c r="B87" t="s">
+        <v>277</v>
+      </c>
+      <c r="C87" t="s">
         <v>278</v>
       </c>
-      <c r="B86" t="s">
+      <c r="D87" t="s">
         <v>279</v>
       </c>
-      <c r="C86" t="s">
-        <v>280</v>
-      </c>
-      <c r="D86" t="s">
-        <v>281</v>
-      </c>
-      <c r="F86" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="G86" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
-        <v>282</v>
-      </c>
-      <c r="B87" t="s">
-        <v>283</v>
-      </c>
-      <c r="C87" t="s">
-        <v>284</v>
-      </c>
-      <c r="D87" t="s">
-        <v>285</v>
-      </c>
       <c r="F87" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B88" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C88" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="D88" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
+        <v>283</v>
+      </c>
+      <c r="B89" t="s">
+        <v>284</v>
+      </c>
+      <c r="C89" t="s">
+        <v>285</v>
+      </c>
+      <c r="D89" t="s">
+        <v>71</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>287</v>
+      </c>
+      <c r="B90" t="s">
+        <v>288</v>
+      </c>
+      <c r="C90" t="s">
         <v>289</v>
       </c>
-      <c r="B89" t="s">
-        <v>290</v>
-      </c>
-      <c r="C89" t="s">
-        <v>291</v>
-      </c>
-      <c r="D89" t="s">
-        <v>73</v>
-      </c>
-      <c r="F89" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="G89" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
-        <v>293</v>
-      </c>
-      <c r="B90" t="s">
-        <v>294</v>
-      </c>
-      <c r="C90" t="s">
-        <v>295</v>
-      </c>
       <c r="D90" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B91" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C91" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="D91" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="G91" s="6"/>
     </row>
     <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B92" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C92" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="D92" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B93" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C93" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="D93" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B94" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C94" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="D94" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G94" s="6"/>
     </row>
     <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B95" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C95" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D95" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
+        <v>306</v>
+      </c>
+      <c r="B96" t="s">
+        <v>307</v>
+      </c>
+      <c r="C96" t="s">
+        <v>308</v>
+      </c>
+      <c r="D96" t="s">
+        <v>305</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>309</v>
+      </c>
+      <c r="B97" t="s">
+        <v>310</v>
+      </c>
+      <c r="C97" t="s">
+        <v>311</v>
+      </c>
+      <c r="D97" t="s">
         <v>312</v>
       </c>
-      <c r="B96" t="s">
-        <v>313</v>
-      </c>
-      <c r="C96" t="s">
-        <v>314</v>
-      </c>
-      <c r="D96" t="s">
-        <v>311</v>
-      </c>
-      <c r="F96" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G96" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
-        <v>315</v>
-      </c>
-      <c r="B97" t="s">
-        <v>316</v>
-      </c>
-      <c r="C97" t="s">
-        <v>317</v>
-      </c>
-      <c r="D97" t="s">
-        <v>318</v>
-      </c>
       <c r="F97" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="7" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B98" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C98" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D98" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F98" s="8"/>
       <c r="G98" s="8"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
+        <v>317</v>
+      </c>
+      <c r="B99" t="s">
+        <v>318</v>
+      </c>
+      <c r="C99" t="s">
+        <v>319</v>
+      </c>
+      <c r="D99" t="s">
+        <v>320</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>321</v>
+      </c>
+      <c r="B100" t="s">
+        <v>322</v>
+      </c>
+      <c r="C100" t="s">
         <v>323</v>
       </c>
-      <c r="B99" t="s">
+      <c r="D100" t="s">
         <v>324</v>
       </c>
-      <c r="C99" t="s">
-        <v>325</v>
-      </c>
-      <c r="D99" t="s">
-        <v>326</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G99" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A100" t="s">
-        <v>327</v>
-      </c>
-      <c r="B100" t="s">
-        <v>328</v>
-      </c>
-      <c r="C100" t="s">
-        <v>329</v>
-      </c>
-      <c r="D100" t="s">
-        <v>330</v>
-      </c>
       <c r="F100" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B101" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C101" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="D101" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G101" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="7" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B102" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C102" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="D102" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="F102" s="8"/>
       <c r="G102" s="8"/>
     </row>
     <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B103" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C103" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="D103" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G103" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B104" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C104" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="D104" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B105" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C105" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="D105" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B106" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C106" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D106" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B107" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="C107" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="D107" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="G107" s="6"/>
     </row>
     <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
+        <v>349</v>
+      </c>
+      <c r="B108" t="s">
+        <v>350</v>
+      </c>
+      <c r="C108" t="s">
+        <v>351</v>
+      </c>
+      <c r="D108" t="s">
+        <v>352</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="G108" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>353</v>
+      </c>
+      <c r="B109" t="s">
+        <v>354</v>
+      </c>
+      <c r="C109" t="s">
         <v>355</v>
       </c>
-      <c r="B108" t="s">
-        <v>356</v>
-      </c>
-      <c r="C108" t="s">
-        <v>357</v>
-      </c>
-      <c r="D108" t="s">
-        <v>358</v>
-      </c>
-      <c r="F108" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="G108" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A109" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="B109" t="s">
-        <v>360</v>
-      </c>
-      <c r="C109" t="s">
-        <v>361</v>
-      </c>
       <c r="D109" t="s">
-        <v>62</v>
-      </c>
-      <c r="F109" s="8"/>
-      <c r="G109" s="8"/>
+        <v>60</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="G109" s="6" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="B110" t="s">
-        <v>363</v>
-      </c>
-      <c r="C110" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="D110" t="s">
-        <v>62</v>
+        <v>262</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>292</v>
+        <v>66</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="B111" t="s">
-        <v>366</v>
+        <v>359</v>
+      </c>
+      <c r="C111" t="s">
+        <v>360</v>
       </c>
       <c r="D111" t="s">
-        <v>268</v>
+        <v>9</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="G111" s="6" t="s">
-        <v>28</v>
+        <v>231</v>
       </c>
     </row>
     <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="B112" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C112" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="D112" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
+        <v>364</v>
+      </c>
+      <c r="B113" t="s">
+        <v>365</v>
+      </c>
+      <c r="C113" t="s">
+        <v>366</v>
+      </c>
+      <c r="D113" t="s">
+        <v>9</v>
+      </c>
+      <c r="F113" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G113" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F114" s="6"/>
+      <c r="G114" s="6"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>367</v>
+      </c>
+      <c r="B115" t="s">
+        <v>368</v>
+      </c>
+      <c r="C115" t="s">
+        <v>369</v>
+      </c>
+      <c r="D115" t="s">
+        <v>71</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G115" s="6"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
         <v>370</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B116" t="s">
         <v>371</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C116" t="s">
         <v>372</v>
       </c>
-      <c r="D113" t="s">
-        <v>62</v>
-      </c>
-      <c r="F113" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G113" s="6" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
+      <c r="D116" t="s">
+        <v>60</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="G116" s="6"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
         <v>373</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B117" t="s">
         <v>374</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C117" t="s">
         <v>375</v>
       </c>
-      <c r="D114" t="s">
+      <c r="D117" t="s">
         <v>9</v>
       </c>
-      <c r="F114" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G114" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F115" s="6"/>
-      <c r="G115" s="6"/>
-    </row>
-    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A116" t="s">
+      <c r="F117" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="G117" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
         <v>376</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B118" t="s">
         <v>377</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C118" t="s">
         <v>378</v>
       </c>
-      <c r="D116" t="s">
-        <v>73</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G116" s="6"/>
-    </row>
-    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A117" t="s">
+      <c r="D118" t="s">
         <v>379</v>
       </c>
-      <c r="B117" t="s">
-        <v>380</v>
-      </c>
-      <c r="C117" t="s">
-        <v>381</v>
-      </c>
-      <c r="D117" t="s">
-        <v>62</v>
-      </c>
-      <c r="F117" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="G117" s="6"/>
-    </row>
-    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A118" t="s">
-        <v>382</v>
-      </c>
-      <c r="B118" t="s">
-        <v>383</v>
-      </c>
-      <c r="C118" t="s">
-        <v>384</v>
-      </c>
-      <c r="D118" t="s">
-        <v>9</v>
-      </c>
       <c r="F118" s="6" t="s">
-        <v>236</v>
+        <v>44</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
+        <v>380</v>
+      </c>
+      <c r="B119" t="s">
+        <v>381</v>
+      </c>
+      <c r="C119" t="s">
+        <v>382</v>
+      </c>
+      <c r="D119" t="s">
+        <v>279</v>
+      </c>
+      <c r="F119" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="G119" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>383</v>
+      </c>
+      <c r="B120" t="s">
+        <v>384</v>
+      </c>
+      <c r="C120" t="s">
         <v>385</v>
       </c>
-      <c r="B119" t="s">
+      <c r="D120" t="s">
         <v>386</v>
       </c>
-      <c r="C119" t="s">
-        <v>387</v>
-      </c>
-      <c r="D119" t="s">
-        <v>388</v>
-      </c>
-      <c r="F119" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G119" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A120" t="s">
-        <v>389</v>
-      </c>
-      <c r="B120" t="s">
-        <v>390</v>
-      </c>
-      <c r="C120" t="s">
-        <v>391</v>
-      </c>
-      <c r="D120" t="s">
-        <v>285</v>
-      </c>
       <c r="F120" s="6" t="s">
-        <v>257</v>
+        <v>44</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
+        <v>387</v>
+      </c>
+      <c r="B121" t="s">
+        <v>388</v>
+      </c>
+      <c r="C121" t="s">
+        <v>389</v>
+      </c>
+      <c r="D121" t="s">
+        <v>390</v>
+      </c>
+      <c r="F121" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G121" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>391</v>
+      </c>
+      <c r="B122" t="s">
         <v>392</v>
       </c>
-      <c r="B121" t="s">
+      <c r="C122" t="s">
         <v>393</v>
       </c>
-      <c r="C121" t="s">
+      <c r="D122" t="s">
         <v>394</v>
       </c>
-      <c r="D121" t="s">
+      <c r="F122" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="G122" s="6"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
         <v>395</v>
       </c>
-      <c r="F121" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G121" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A122" t="s">
+      <c r="B123" t="s">
         <v>396</v>
       </c>
-      <c r="B122" t="s">
+      <c r="C123" t="s">
         <v>397</v>
       </c>
-      <c r="C122" t="s">
+      <c r="D123" t="s">
         <v>398</v>
       </c>
-      <c r="D122" t="s">
+      <c r="F123" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="G123" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
         <v>399</v>
       </c>
-      <c r="F122" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G122" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A123" t="s">
+      <c r="B124" t="s">
         <v>400</v>
       </c>
-      <c r="B123" t="s">
+      <c r="C124" t="s">
         <v>401</v>
       </c>
-      <c r="C123" t="s">
+      <c r="D124" t="s">
+        <v>133</v>
+      </c>
+      <c r="F124" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G124" s="6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
         <v>402</v>
       </c>
-      <c r="D123" t="s">
+      <c r="B125" t="s">
         <v>403</v>
       </c>
-      <c r="F123" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="G123" s="6"/>
-    </row>
-    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A124" t="s">
+      <c r="C125" t="s">
         <v>404</v>
       </c>
-      <c r="B124" t="s">
+      <c r="D125" t="s">
         <v>405</v>
       </c>
-      <c r="C124" t="s">
+      <c r="F125" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G125" s="6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
         <v>406</v>
       </c>
-      <c r="D124" t="s">
+      <c r="B126" t="s">
         <v>407</v>
       </c>
-      <c r="F124" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="G124" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A125" t="s">
+      <c r="C126" t="s">
         <v>408</v>
       </c>
-      <c r="B125" t="s">
+      <c r="D126" t="s">
+        <v>76</v>
+      </c>
+      <c r="F126" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G126" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
         <v>409</v>
       </c>
-      <c r="C125" t="s">
+      <c r="B127" t="s">
         <v>410</v>
       </c>
-      <c r="D125" t="s">
-        <v>135</v>
-      </c>
-      <c r="F125" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G125" s="6" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A126" t="s">
+      <c r="C127" t="s">
         <v>411</v>
       </c>
-      <c r="B126" t="s">
+      <c r="D127" t="s">
         <v>412</v>
       </c>
-      <c r="C126" t="s">
+      <c r="F127" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G127" s="6"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A128" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="D126" t="s">
+      <c r="B128" t="s">
         <v>414</v>
       </c>
-      <c r="F126" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G126" s="6" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A127" t="s">
+      <c r="D128" t="s">
+        <v>262</v>
+      </c>
+      <c r="F128" s="8"/>
+      <c r="G128" s="8"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
         <v>415</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B129" t="s">
         <v>416</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C129" t="s">
         <v>417</v>
       </c>
-      <c r="D127" t="s">
-        <v>78</v>
-      </c>
-      <c r="F127" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G127" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A128" t="s">
+      <c r="D129" t="s">
         <v>418</v>
       </c>
-      <c r="B128" t="s">
+      <c r="F129" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="G129" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
         <v>419</v>
       </c>
-      <c r="C128" t="s">
+      <c r="B130" t="s">
         <v>420</v>
       </c>
-      <c r="D128" t="s">
+      <c r="C130" t="s">
         <v>421</v>
       </c>
-      <c r="F128" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G128" s="6"/>
-    </row>
-    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="7" t="s">
+      <c r="D130" t="s">
         <v>422</v>
       </c>
-      <c r="B129" t="s">
-        <v>423</v>
-      </c>
-      <c r="D129" t="s">
-        <v>268</v>
-      </c>
-      <c r="F129" s="8"/>
-      <c r="G129" s="8"/>
-    </row>
-    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A130" t="s">
-        <v>424</v>
-      </c>
-      <c r="B130" t="s">
-        <v>425</v>
-      </c>
-      <c r="C130" t="s">
-        <v>426</v>
-      </c>
-      <c r="D130" t="s">
-        <v>427</v>
-      </c>
       <c r="F130" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="G130" s="6" t="s">
-        <v>28</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="G130" s="6"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
+        <v>423</v>
+      </c>
+      <c r="B131" t="s">
+        <v>424</v>
+      </c>
+      <c r="C131" t="s">
+        <v>425</v>
+      </c>
+      <c r="D131" t="s">
+        <v>426</v>
+      </c>
+      <c r="F131" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G131" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>427</v>
+      </c>
+      <c r="B132" t="s">
         <v>428</v>
       </c>
-      <c r="B131" t="s">
+      <c r="C132" t="s">
         <v>429</v>
       </c>
-      <c r="C131" t="s">
+      <c r="D132" t="s">
+        <v>238</v>
+      </c>
+      <c r="F132" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="G132" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
         <v>430</v>
       </c>
-      <c r="D131" t="s">
+      <c r="B133" t="s">
         <v>431</v>
       </c>
-      <c r="F131" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G131" s="6"/>
-    </row>
-    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A132" t="s">
+      <c r="C133" t="s">
         <v>432</v>
       </c>
-      <c r="B132" t="s">
+      <c r="D133" t="s">
         <v>433</v>
       </c>
-      <c r="C132" t="s">
+      <c r="F133" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G133" s="6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
         <v>434</v>
       </c>
-      <c r="D132" t="s">
+      <c r="B134" t="s">
         <v>435</v>
       </c>
-      <c r="F132" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G132" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A133" t="s">
+      <c r="C134" t="s">
         <v>436</v>
       </c>
-      <c r="B133" t="s">
+      <c r="D134" t="s">
         <v>437</v>
       </c>
-      <c r="C133" t="s">
+      <c r="F134" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="G134" s="6"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="7" t="s">
         <v>438</v>
       </c>
-      <c r="D133" t="s">
-        <v>243</v>
-      </c>
-      <c r="F133" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="G133" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A134" t="s">
+      <c r="B135" t="s">
         <v>439</v>
       </c>
-      <c r="B134" t="s">
+      <c r="C135" t="s">
         <v>440</v>
       </c>
-      <c r="C134" t="s">
+      <c r="D135" t="s">
         <v>441</v>
       </c>
-      <c r="D134" t="s">
+      <c r="F135" s="8"/>
+      <c r="G135" s="8"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
         <v>442</v>
       </c>
-      <c r="F134" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G134" s="6" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A135" t="s">
+      <c r="B136" t="s">
         <v>443</v>
       </c>
-      <c r="B135" t="s">
+      <c r="C136" t="s">
+        <v>443</v>
+      </c>
+      <c r="D136" t="s">
         <v>444</v>
       </c>
-      <c r="C135" t="s">
+      <c r="F136" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="G136" s="6"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
         <v>445</v>
       </c>
-      <c r="D135" t="s">
+      <c r="B137" t="s">
         <v>446</v>
       </c>
-      <c r="F135" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="G135" s="6"/>
-    </row>
-    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="7" t="s">
+      <c r="C137" t="s">
         <v>447</v>
       </c>
-      <c r="B136" t="s">
-        <v>448</v>
-      </c>
-      <c r="C136" t="s">
-        <v>449</v>
-      </c>
-      <c r="D136" t="s">
-        <v>450</v>
-      </c>
-      <c r="F136" s="8"/>
-      <c r="G136" s="8"/>
-    </row>
-    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A137" t="s">
-        <v>451</v>
-      </c>
-      <c r="B137" t="s">
-        <v>452</v>
-      </c>
-      <c r="C137" t="s">
-        <v>452</v>
-      </c>
       <c r="D137" t="s">
-        <v>453</v>
+        <v>133</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="G137" s="6"/>
+        <v>13</v>
+      </c>
+      <c r="G137" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
+        <v>448</v>
+      </c>
+      <c r="B138" t="s">
+        <v>449</v>
+      </c>
+      <c r="C138" t="s">
+        <v>450</v>
+      </c>
+      <c r="D138" t="s">
+        <v>133</v>
+      </c>
+      <c r="F138" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G138" s="6"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>451</v>
+      </c>
+      <c r="B139" t="s">
+        <v>452</v>
+      </c>
+      <c r="C139" t="s">
+        <v>453</v>
+      </c>
+      <c r="D139" t="s">
+        <v>305</v>
+      </c>
+      <c r="F139" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G139" s="6"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
         <v>454</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B140" t="s">
         <v>455</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C140" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="D138" t="s">
-        <v>135</v>
-      </c>
-      <c r="F138" s="6" t="s">
+      <c r="D140" t="s">
+        <v>113</v>
+      </c>
+      <c r="F140" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G140" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>457</v>
+      </c>
+      <c r="C141" t="s">
+        <v>458</v>
+      </c>
+      <c r="D141" t="s">
+        <v>459</v>
+      </c>
+      <c r="F141" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G141" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G138" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A139" t="s">
-        <v>457</v>
-      </c>
-      <c r="B139" t="s">
-        <v>458</v>
-      </c>
-      <c r="C139" t="s">
-        <v>459</v>
-      </c>
-      <c r="D139" t="s">
-        <v>135</v>
-      </c>
-      <c r="F139" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G139" s="6"/>
-    </row>
-    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A140" t="s">
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
         <v>460</v>
       </c>
-      <c r="B140" t="s">
+      <c r="C142" t="s">
         <v>461</v>
       </c>
-      <c r="C140" t="s">
+      <c r="D142" t="s">
+        <v>60</v>
+      </c>
+      <c r="F142" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="G142" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
         <v>462</v>
       </c>
-      <c r="D140" t="s">
-        <v>311</v>
-      </c>
-      <c r="F140" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G140" s="6"/>
-    </row>
-    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A141" t="s">
+      <c r="C143" t="s">
         <v>463</v>
       </c>
-      <c r="B141" t="s">
+      <c r="D143" t="s">
         <v>464</v>
       </c>
-      <c r="C141" s="2" t="s">
+      <c r="F143" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G143" s="6"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
         <v>465</v>
       </c>
-      <c r="D141" t="s">
-        <v>115</v>
-      </c>
-      <c r="F141" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G141" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A142" t="s">
+      <c r="C144" t="s">
         <v>466</v>
       </c>
-      <c r="C142" t="s">
+      <c r="D144" t="s">
+        <v>76</v>
+      </c>
+      <c r="F144" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G144" s="6"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
         <v>467</v>
       </c>
-      <c r="D142" t="s">
+      <c r="C145" t="s">
         <v>468</v>
       </c>
-      <c r="F142" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G142" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A143" t="s">
-        <v>469</v>
-      </c>
-      <c r="C143" t="s">
-        <v>470</v>
-      </c>
-      <c r="D143" t="s">
-        <v>62</v>
-      </c>
-      <c r="F143" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G143" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A144" t="s">
-        <v>471</v>
-      </c>
-      <c r="C144" t="s">
-        <v>472</v>
-      </c>
-      <c r="D144" t="s">
-        <v>473</v>
-      </c>
-      <c r="F144" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G144" s="6"/>
-    </row>
-    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A145" t="s">
-        <v>474</v>
-      </c>
-      <c r="C145" t="s">
-        <v>475</v>
-      </c>
       <c r="D145" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="F145" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G145" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="G145" s="6" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="C146" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="D146" t="s">
-        <v>62</v>
+        <v>471</v>
       </c>
       <c r="F146" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G146" s="6" t="s">
-        <v>74</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G146" s="6"/>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="C147" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="D147" t="s">
-        <v>480</v>
+        <v>60</v>
       </c>
       <c r="F147" s="6" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="G147" s="6"/>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
+        <v>474</v>
+      </c>
+      <c r="C148" t="s">
+        <v>475</v>
+      </c>
+      <c r="D148" t="s">
+        <v>76</v>
+      </c>
+      <c r="F148" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G148" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>476</v>
+      </c>
+      <c r="C149" t="s">
+        <v>477</v>
+      </c>
+      <c r="D149" t="s">
+        <v>76</v>
+      </c>
+      <c r="F149" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G149" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>478</v>
+      </c>
+      <c r="C150" t="s">
+        <v>479</v>
+      </c>
+      <c r="D150" t="s">
+        <v>166</v>
+      </c>
+      <c r="F150" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G150" s="6"/>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>480</v>
+      </c>
+      <c r="C151" t="s">
         <v>481</v>
       </c>
-      <c r="C148" t="s">
+      <c r="D151" t="s">
+        <v>166</v>
+      </c>
+      <c r="F151" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G151" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
         <v>482</v>
       </c>
-      <c r="D148" t="s">
-        <v>62</v>
-      </c>
-      <c r="F148" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G148" s="6"/>
-    </row>
-    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A149" t="s">
+      <c r="C152" t="s">
         <v>483</v>
       </c>
-      <c r="C149" t="s">
+      <c r="D152" t="s">
+        <v>76</v>
+      </c>
+      <c r="F152" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G152" s="6"/>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
         <v>484</v>
       </c>
-      <c r="D149" t="s">
-        <v>78</v>
-      </c>
-      <c r="F149" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G149" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A150" t="s">
+      <c r="C153" t="s">
         <v>485</v>
       </c>
-      <c r="C150" t="s">
+      <c r="D153" t="s">
+        <v>9</v>
+      </c>
+      <c r="F153" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G153" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
         <v>486</v>
       </c>
-      <c r="D150" t="s">
-        <v>78</v>
-      </c>
-      <c r="F150" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G150" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A151" t="s">
+      <c r="C154" t="s">
         <v>487</v>
       </c>
-      <c r="C151" t="s">
+      <c r="D154" t="s">
+        <v>76</v>
+      </c>
+      <c r="F154" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G154" s="6"/>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
         <v>488</v>
       </c>
-      <c r="D151" t="s">
-        <v>168</v>
-      </c>
-      <c r="F151" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G151" s="6"/>
-    </row>
-    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A152" t="s">
+      <c r="C155" t="s">
         <v>489</v>
       </c>
-      <c r="C152" t="s">
+      <c r="D155" t="s">
+        <v>166</v>
+      </c>
+      <c r="F155" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G155" s="6"/>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
         <v>490</v>
       </c>
-      <c r="D152" t="s">
-        <v>168</v>
-      </c>
-      <c r="F152" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="G152" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A153" t="s">
+      <c r="C156" t="s">
         <v>491</v>
       </c>
-      <c r="C153" t="s">
+      <c r="D156" t="s">
+        <v>166</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="G156" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
         <v>492</v>
       </c>
-      <c r="D153" t="s">
-        <v>78</v>
-      </c>
-      <c r="F153" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G153" s="6"/>
-    </row>
-    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A154" t="s">
+      <c r="C157" t="s">
         <v>493</v>
       </c>
-      <c r="C154" t="s">
+      <c r="D157" t="s">
+        <v>133</v>
+      </c>
+      <c r="F157" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G157" s="6"/>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
         <v>494</v>
       </c>
-      <c r="D154" t="s">
+      <c r="C158" t="s">
+        <v>495</v>
+      </c>
+      <c r="D158" t="s">
+        <v>25</v>
+      </c>
+      <c r="F158" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G158" s="6"/>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
+        <v>496</v>
+      </c>
+      <c r="C159" t="s">
+        <v>497</v>
+      </c>
+      <c r="D159" t="s">
         <v>9</v>
       </c>
-      <c r="F154" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="G154" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A155" t="s">
-        <v>495</v>
-      </c>
-      <c r="C155" t="s">
-        <v>496</v>
-      </c>
-      <c r="D155" t="s">
-        <v>78</v>
-      </c>
-      <c r="F155" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G155" s="6"/>
-    </row>
-    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A156" t="s">
-        <v>497</v>
-      </c>
-      <c r="C156" t="s">
+      <c r="F159" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G159" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
         <v>498</v>
       </c>
-      <c r="D156" t="s">
-        <v>168</v>
-      </c>
-      <c r="F156" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G156" s="6"/>
-    </row>
-    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A157" t="s">
+      <c r="C160" t="s">
         <v>499</v>
       </c>
-      <c r="C157" t="s">
+      <c r="D160" t="s">
+        <v>60</v>
+      </c>
+      <c r="F160" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G160" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
         <v>500</v>
       </c>
-      <c r="D157" t="s">
-        <v>168</v>
-      </c>
-      <c r="F157" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="G157" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A158" t="s">
+      <c r="C161" t="s">
         <v>501</v>
       </c>
-      <c r="C158" t="s">
+      <c r="D161" t="s">
+        <v>76</v>
+      </c>
+      <c r="F161" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G161" s="6"/>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
         <v>502</v>
       </c>
-      <c r="D158" t="s">
-        <v>135</v>
-      </c>
-      <c r="F158" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G158" s="6"/>
-    </row>
-    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A159" t="s">
+      <c r="C162" t="s">
         <v>503</v>
       </c>
-      <c r="C159" t="s">
+      <c r="D162" t="s">
+        <v>76</v>
+      </c>
+      <c r="F162" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G162" s="6"/>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
         <v>504</v>
       </c>
-      <c r="D159" t="s">
+      <c r="C163" t="s">
+        <v>505</v>
+      </c>
+      <c r="D163" t="s">
+        <v>76</v>
+      </c>
+      <c r="F163" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G163" s="6"/>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>506</v>
+      </c>
+      <c r="C164" t="s">
+        <v>507</v>
+      </c>
+      <c r="D164" t="s">
+        <v>60</v>
+      </c>
+      <c r="F164" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G164" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>508</v>
+      </c>
+      <c r="C165" t="s">
+        <v>509</v>
+      </c>
+      <c r="D165" t="s">
+        <v>76</v>
+      </c>
+      <c r="F165" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G165" s="6"/>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
+        <v>510</v>
+      </c>
+      <c r="C166" t="s">
+        <v>511</v>
+      </c>
+      <c r="D166" t="s">
+        <v>53</v>
+      </c>
+      <c r="F166" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F159" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G159" s="6"/>
-    </row>
-    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A160" t="s">
-        <v>505</v>
-      </c>
-      <c r="C160" t="s">
-        <v>506</v>
-      </c>
-      <c r="D160" t="s">
-        <v>9</v>
-      </c>
-      <c r="F160" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G160" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A161" t="s">
-        <v>507</v>
-      </c>
-      <c r="C161" t="s">
-        <v>508</v>
-      </c>
-      <c r="D161" t="s">
-        <v>62</v>
-      </c>
-      <c r="F161" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G161" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A162" t="s">
-        <v>509</v>
-      </c>
-      <c r="C162" t="s">
-        <v>510</v>
-      </c>
-      <c r="D162" t="s">
-        <v>78</v>
-      </c>
-      <c r="F162" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G162" s="6"/>
-    </row>
-    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A163" t="s">
-        <v>511</v>
-      </c>
-      <c r="C163" t="s">
+      <c r="G166" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A167" t="s">
         <v>512</v>
       </c>
-      <c r="D163" t="s">
-        <v>78</v>
-      </c>
-      <c r="F163" s="6" t="s">
+      <c r="C167" t="s">
+        <v>513</v>
+      </c>
+      <c r="D167" t="s">
+        <v>514</v>
+      </c>
+      <c r="F167" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G167" s="6"/>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
+        <v>515</v>
+      </c>
+      <c r="C168" t="s">
+        <v>516</v>
+      </c>
+      <c r="D168" t="s">
+        <v>166</v>
+      </c>
+      <c r="F168" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G163" s="6"/>
-    </row>
-    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A164" t="s">
-        <v>513</v>
-      </c>
-      <c r="C164" t="s">
-        <v>514</v>
-      </c>
-      <c r="D164" t="s">
-        <v>78</v>
-      </c>
-      <c r="F164" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G164" s="6"/>
-    </row>
-    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A165" t="s">
-        <v>515</v>
-      </c>
-      <c r="C165" t="s">
-        <v>516</v>
-      </c>
-      <c r="D165" t="s">
-        <v>62</v>
-      </c>
-      <c r="F165" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G165" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A166" t="s">
+      <c r="G168" s="6"/>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
         <v>517</v>
       </c>
-      <c r="C166" t="s">
+      <c r="C169" t="s">
         <v>518</v>
       </c>
-      <c r="D166" t="s">
-        <v>78</v>
-      </c>
-      <c r="F166" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G166" s="6"/>
-    </row>
-    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A167" t="s">
+      <c r="D169" t="s">
         <v>519</v>
-      </c>
-      <c r="C167" t="s">
-        <v>520</v>
-      </c>
-      <c r="D167" t="s">
-        <v>55</v>
-      </c>
-      <c r="F167" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G167" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A168" t="s">
-        <v>521</v>
-      </c>
-      <c r="C168" t="s">
-        <v>522</v>
-      </c>
-      <c r="D168" t="s">
-        <v>523</v>
-      </c>
-      <c r="F168" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G168" s="6"/>
-    </row>
-    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A169" t="s">
-        <v>524</v>
-      </c>
-      <c r="C169" t="s">
-        <v>525</v>
-      </c>
-      <c r="D169" t="s">
-        <v>168</v>
       </c>
       <c r="F169" s="6" t="s">
         <v>10</v>
       </c>
       <c r="G169" s="6"/>
     </row>
-    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
+        <v>520</v>
+      </c>
+      <c r="C170" t="s">
+        <v>521</v>
+      </c>
+      <c r="D170" t="s">
+        <v>76</v>
+      </c>
+      <c r="F170" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="G170" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A171" t="s">
+        <v>522</v>
+      </c>
+      <c r="C171" t="s">
+        <v>523</v>
+      </c>
+      <c r="D171" t="s">
+        <v>76</v>
+      </c>
+      <c r="F171" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G171" s="6"/>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A172" t="s">
+        <v>524</v>
+      </c>
+      <c r="C172" t="s">
+        <v>525</v>
+      </c>
+      <c r="D172" t="s">
+        <v>166</v>
+      </c>
+      <c r="F172" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G172" s="6"/>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A173" t="s">
         <v>526</v>
       </c>
-      <c r="C170" t="s">
+      <c r="C173" t="s">
         <v>527</v>
       </c>
-      <c r="D170" t="s">
+      <c r="D173" t="s">
+        <v>76</v>
+      </c>
+      <c r="F173" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G173" s="6"/>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
         <v>528</v>
       </c>
-      <c r="F170" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G170" s="6"/>
-    </row>
-    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A171" t="s">
+      <c r="C174" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="C171" t="s">
+      <c r="D174" t="s">
+        <v>166</v>
+      </c>
+      <c r="F174" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G174" s="6"/>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
         <v>530</v>
       </c>
-      <c r="D171" t="s">
-        <v>78</v>
-      </c>
-      <c r="F171" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G171" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A172" t="s">
+      <c r="C175" t="s">
         <v>531</v>
       </c>
-      <c r="C172" t="s">
-        <v>532</v>
-      </c>
-      <c r="D172" t="s">
-        <v>78</v>
-      </c>
-      <c r="F172" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G172" s="6"/>
-    </row>
-    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A173" t="s">
-        <v>533</v>
-      </c>
-      <c r="C173" t="s">
-        <v>534</v>
-      </c>
-      <c r="D173" t="s">
-        <v>168</v>
-      </c>
-      <c r="F173" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G173" s="6"/>
-    </row>
-    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A174" t="s">
-        <v>535</v>
-      </c>
-      <c r="C174" t="s">
-        <v>536</v>
-      </c>
-      <c r="D174" t="s">
-        <v>78</v>
-      </c>
-      <c r="F174" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G174" s="6"/>
-    </row>
-    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A175" t="s">
-        <v>537</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>538</v>
-      </c>
       <c r="D175" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F175" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G175" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="G175" s="6" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
+        <v>532</v>
+      </c>
+      <c r="C176" t="s">
+        <v>533</v>
+      </c>
+      <c r="D176" t="s">
+        <v>166</v>
+      </c>
+      <c r="F176" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G176" s="6"/>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A177" t="s">
+        <v>534</v>
+      </c>
+      <c r="C177" t="s">
+        <v>535</v>
+      </c>
+      <c r="D177" t="s">
+        <v>166</v>
+      </c>
+      <c r="F177" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G177" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A178" t="s">
+        <v>536</v>
+      </c>
+      <c r="C178" t="s">
+        <v>537</v>
+      </c>
+      <c r="D178" t="s">
+        <v>60</v>
+      </c>
+      <c r="F178" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G178" s="6"/>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A179" t="s">
+        <v>538</v>
+      </c>
+      <c r="C179" t="s">
         <v>539</v>
       </c>
-      <c r="C176" t="s">
+      <c r="D179" t="s">
+        <v>166</v>
+      </c>
+      <c r="F179" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G179" s="6"/>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
         <v>540</v>
       </c>
-      <c r="D176" t="s">
-        <v>168</v>
-      </c>
-      <c r="F176" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G176" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A177" t="s">
+      <c r="C180" t="s">
         <v>541</v>
       </c>
-      <c r="C177" t="s">
+      <c r="D180" t="s">
+        <v>76</v>
+      </c>
+      <c r="F180" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G180" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A181" t="s">
         <v>542</v>
       </c>
-      <c r="D177" t="s">
-        <v>168</v>
-      </c>
-      <c r="F177" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G177" s="6"/>
-    </row>
-    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A178" t="s">
+      <c r="C181" t="s">
         <v>543</v>
       </c>
-      <c r="C178" t="s">
+      <c r="D181" t="s">
+        <v>60</v>
+      </c>
+      <c r="F181" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G181" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F182" s="6"/>
+      <c r="G182" s="6"/>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
         <v>544</v>
       </c>
-      <c r="D178" t="s">
-        <v>168</v>
-      </c>
-      <c r="F178" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G178" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A179" t="s">
+      <c r="C183" t="s">
         <v>545</v>
       </c>
-      <c r="C179" t="s">
+      <c r="D183" t="s">
+        <v>76</v>
+      </c>
+      <c r="F183" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="G183" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
         <v>546</v>
       </c>
-      <c r="D179" t="s">
-        <v>62</v>
-      </c>
-      <c r="F179" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G179" s="6"/>
-    </row>
-    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A180" t="s">
+      <c r="C184" t="s">
         <v>547</v>
       </c>
-      <c r="C180" t="s">
+      <c r="D184" t="s">
+        <v>166</v>
+      </c>
+      <c r="F184" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G184" s="6"/>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A185" t="s">
         <v>548</v>
       </c>
-      <c r="D180" t="s">
-        <v>168</v>
-      </c>
-      <c r="F180" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G180" s="6"/>
-    </row>
-    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A181" t="s">
+      <c r="C185" t="s">
         <v>549</v>
       </c>
-      <c r="C181" t="s">
+      <c r="D185" t="s">
+        <v>464</v>
+      </c>
+      <c r="F185" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G185" s="6"/>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A186" t="s">
         <v>550</v>
       </c>
-      <c r="D181" t="s">
-        <v>78</v>
-      </c>
-      <c r="F181" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G181" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A182" t="s">
+      <c r="C186" t="s">
         <v>551</v>
       </c>
-      <c r="C182" t="s">
+      <c r="D186" t="s">
+        <v>9</v>
+      </c>
+      <c r="F186" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G186" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A187" t="s">
         <v>552</v>
       </c>
-      <c r="D182" t="s">
-        <v>62</v>
-      </c>
-      <c r="F182" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G182" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F183" s="6"/>
-      <c r="G183" s="6"/>
-    </row>
-    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A184" t="s">
+      <c r="C187" t="s">
         <v>553</v>
       </c>
-      <c r="C184" t="s">
+      <c r="D187" t="s">
+        <v>76</v>
+      </c>
+      <c r="F187" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G187" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A188" t="s">
         <v>554</v>
       </c>
-      <c r="D184" t="s">
-        <v>78</v>
-      </c>
-      <c r="F184" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="G184" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A185" t="s">
+      <c r="C188" t="s">
         <v>555</v>
       </c>
-      <c r="C185" t="s">
+      <c r="D188" t="s">
+        <v>76</v>
+      </c>
+      <c r="F188" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G188" s="6"/>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A189" t="s">
         <v>556</v>
       </c>
-      <c r="D185" t="s">
-        <v>168</v>
-      </c>
-      <c r="F185" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G185" s="6"/>
-    </row>
-    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A186" t="s">
+      <c r="C189" t="s">
         <v>557</v>
       </c>
-      <c r="C186" t="s">
-        <v>558</v>
-      </c>
-      <c r="D186" t="s">
-        <v>473</v>
-      </c>
-      <c r="F186" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G186" s="6"/>
-    </row>
-    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A187" t="s">
-        <v>559</v>
-      </c>
-      <c r="C187" t="s">
-        <v>560</v>
-      </c>
-      <c r="D187" t="s">
-        <v>9</v>
-      </c>
-      <c r="F187" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G187" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A188" t="s">
-        <v>561</v>
-      </c>
-      <c r="C188" t="s">
-        <v>562</v>
-      </c>
-      <c r="D188" t="s">
-        <v>78</v>
-      </c>
-      <c r="F188" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G188" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A189" t="s">
-        <v>563</v>
-      </c>
-      <c r="C189" t="s">
-        <v>564</v>
-      </c>
       <c r="D189" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G189" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="G189" s="6" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
+        <v>558</v>
+      </c>
+      <c r="C190" t="s">
+        <v>559</v>
+      </c>
+      <c r="D190" t="s">
+        <v>53</v>
+      </c>
+      <c r="F190" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G190" s="6"/>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A191" t="s">
+        <v>560</v>
+      </c>
+      <c r="C191" t="s">
+        <v>561</v>
+      </c>
+      <c r="D191" t="s">
+        <v>459</v>
+      </c>
+      <c r="F191" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G191" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
+        <v>562</v>
+      </c>
+      <c r="C192" t="s">
+        <v>563</v>
+      </c>
+      <c r="D192" t="s">
+        <v>166</v>
+      </c>
+      <c r="F192" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="G192" s="6"/>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
+        <v>564</v>
+      </c>
+      <c r="C193" t="s">
         <v>565</v>
       </c>
-      <c r="C190" t="s">
+      <c r="D193" t="s">
+        <v>166</v>
+      </c>
+      <c r="F193" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G193" s="6"/>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A194" t="s">
         <v>566</v>
       </c>
-      <c r="D190" t="s">
-        <v>62</v>
-      </c>
-      <c r="F190" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G190" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A191" t="s">
+      <c r="C194" t="s">
         <v>567</v>
       </c>
-      <c r="C191" t="s">
+      <c r="D194" t="s">
+        <v>60</v>
+      </c>
+      <c r="F194" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G194" s="6"/>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A195" t="s">
         <v>568</v>
       </c>
-      <c r="D191" t="s">
-        <v>55</v>
-      </c>
-      <c r="F191" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G191" s="6"/>
-    </row>
-    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A192" t="s">
+      <c r="C195" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="C192" t="s">
+      <c r="D195" t="s">
+        <v>166</v>
+      </c>
+      <c r="F195" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G195" s="6"/>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A196" t="s">
         <v>570</v>
       </c>
-      <c r="D192" t="s">
-        <v>468</v>
-      </c>
-      <c r="F192" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G192" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A193" t="s">
+      <c r="C196" t="s">
         <v>571</v>
       </c>
-      <c r="C193" t="s">
+      <c r="D196" t="s">
+        <v>113</v>
+      </c>
+      <c r="F196" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G196" s="6"/>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A197" t="s">
         <v>572</v>
       </c>
-      <c r="D193" t="s">
-        <v>168</v>
-      </c>
-      <c r="F193" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="G193" s="6"/>
-    </row>
-    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A194" t="s">
+      <c r="C197" t="s">
         <v>573</v>
       </c>
-      <c r="C194" t="s">
+      <c r="D197" t="s">
+        <v>60</v>
+      </c>
+      <c r="F197" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="G197" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A198" t="s">
         <v>574</v>
       </c>
-      <c r="D194" t="s">
-        <v>168</v>
-      </c>
-      <c r="F194" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G194" s="6"/>
-    </row>
-    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A195" t="s">
+      <c r="C198" t="s">
         <v>575</v>
       </c>
-      <c r="C195" t="s">
+      <c r="D198" t="s">
+        <v>166</v>
+      </c>
+      <c r="F198" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G198" s="6"/>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
         <v>576</v>
       </c>
-      <c r="D195" t="s">
-        <v>62</v>
-      </c>
-      <c r="F195" s="6" t="s">
+      <c r="C199" t="s">
+        <v>577</v>
+      </c>
+      <c r="D199" t="s">
+        <v>166</v>
+      </c>
+      <c r="F199" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="G199" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A200" t="s">
+        <v>578</v>
+      </c>
+      <c r="C200" t="s">
+        <v>579</v>
+      </c>
+      <c r="D200" t="s">
+        <v>60</v>
+      </c>
+      <c r="F200" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G200" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A201" t="s">
+        <v>580</v>
+      </c>
+      <c r="C201" t="s">
+        <v>581</v>
+      </c>
+      <c r="D201" t="s">
+        <v>25</v>
+      </c>
+      <c r="F201" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G201" s="6"/>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A202" t="s">
+        <v>582</v>
+      </c>
+      <c r="C202" t="s">
+        <v>583</v>
+      </c>
+      <c r="D202" t="s">
+        <v>71</v>
+      </c>
+      <c r="F202" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G195" s="6"/>
-    </row>
-    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A196" t="s">
-        <v>577</v>
-      </c>
-      <c r="C196" t="s">
-        <v>578</v>
-      </c>
-      <c r="D196" t="s">
-        <v>168</v>
-      </c>
-      <c r="F196" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G196" s="6"/>
-    </row>
-    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A197" t="s">
-        <v>579</v>
-      </c>
-      <c r="C197" t="s">
-        <v>580</v>
-      </c>
-      <c r="D197" t="s">
-        <v>115</v>
-      </c>
-      <c r="F197" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G197" s="6"/>
-    </row>
-    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A198" t="s">
-        <v>581</v>
-      </c>
-      <c r="C198" t="s">
-        <v>582</v>
-      </c>
-      <c r="D198" t="s">
-        <v>62</v>
-      </c>
-      <c r="F198" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G198" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A199" t="s">
-        <v>583</v>
-      </c>
-      <c r="C199" t="s">
+      <c r="G202" s="6"/>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A203" t="s">
         <v>584</v>
       </c>
-      <c r="D199" t="s">
-        <v>168</v>
-      </c>
-      <c r="F199" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G199" s="6"/>
-    </row>
-    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A200" t="s">
+      <c r="C203" t="s">
         <v>585</v>
       </c>
-      <c r="C200" t="s">
+      <c r="D203" t="s">
+        <v>166</v>
+      </c>
+      <c r="F203" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G203" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A204" t="s">
         <v>586</v>
       </c>
-      <c r="D200" t="s">
-        <v>168</v>
-      </c>
-      <c r="F200" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="G200" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A201" t="s">
+      <c r="C204" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="C201" t="s">
-        <v>588</v>
-      </c>
-      <c r="D201" t="s">
-        <v>62</v>
-      </c>
-      <c r="F201" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G201" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A202" t="s">
-        <v>589</v>
-      </c>
-      <c r="C202" t="s">
-        <v>590</v>
-      </c>
-      <c r="D202" t="s">
-        <v>27</v>
-      </c>
-      <c r="F202" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G202" s="6"/>
-    </row>
-    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A203" t="s">
-        <v>591</v>
-      </c>
-      <c r="C203" t="s">
-        <v>592</v>
-      </c>
-      <c r="D203" t="s">
-        <v>73</v>
-      </c>
-      <c r="F203" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G203" s="6"/>
-    </row>
-    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A204" t="s">
-        <v>593</v>
-      </c>
-      <c r="C204" t="s">
-        <v>594</v>
-      </c>
       <c r="D204" t="s">
-        <v>168</v>
+        <v>9</v>
       </c>
       <c r="F204" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G204" s="6" t="s">
-        <v>74</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="G204" s="6"/>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
+        <v>588</v>
+      </c>
+      <c r="C205" t="s">
+        <v>589</v>
+      </c>
+      <c r="D205" t="s">
+        <v>60</v>
+      </c>
+      <c r="F205" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G205" s="6"/>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A206" t="s">
+        <v>590</v>
+      </c>
+      <c r="C206" t="s">
+        <v>591</v>
+      </c>
+      <c r="D206" t="s">
+        <v>17</v>
+      </c>
+      <c r="F206" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G206" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A207" t="s">
+        <v>592</v>
+      </c>
+      <c r="C207" t="s">
+        <v>593</v>
+      </c>
+      <c r="D207" t="s">
+        <v>71</v>
+      </c>
+      <c r="F207" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G207" s="6"/>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A208" t="s">
+        <v>594</v>
+      </c>
+      <c r="C208" t="s">
         <v>595</v>
       </c>
-      <c r="C205" s="2" t="s">
+      <c r="D208" t="s">
+        <v>133</v>
+      </c>
+      <c r="F208" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G208" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A209" t="s">
         <v>596</v>
       </c>
-      <c r="D205" t="s">
+      <c r="C209" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="D209" t="s">
+        <v>166</v>
+      </c>
+      <c r="F209" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G209" s="6"/>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A210" t="s">
+        <v>598</v>
+      </c>
+      <c r="C210" t="s">
+        <v>599</v>
+      </c>
+      <c r="D210" t="s">
+        <v>600</v>
+      </c>
+      <c r="F210" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G210" s="6"/>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A211" t="s">
+        <v>601</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="D211" t="s">
+        <v>166</v>
+      </c>
+      <c r="F211" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G211" s="6"/>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A212" t="s">
+        <v>602</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="D212" t="s">
+        <v>604</v>
+      </c>
+      <c r="F212" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G212" s="6"/>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A213" t="s">
+        <v>605</v>
+      </c>
+      <c r="C213" t="s">
+        <v>606</v>
+      </c>
+      <c r="D213" t="s">
+        <v>53</v>
+      </c>
+      <c r="F213" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G213" s="6"/>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A214" t="s">
+        <v>607</v>
+      </c>
+      <c r="C214" t="s">
+        <v>608</v>
+      </c>
+      <c r="D214" t="s">
         <v>9</v>
       </c>
-      <c r="F205" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G205" s="6"/>
-    </row>
-    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A206" t="s">
-        <v>597</v>
-      </c>
-      <c r="C206" t="s">
-        <v>598</v>
-      </c>
-      <c r="D206" t="s">
-        <v>62</v>
-      </c>
-      <c r="F206" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G206" s="6"/>
-    </row>
-    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A207" t="s">
-        <v>599</v>
-      </c>
-      <c r="C207" t="s">
-        <v>600</v>
-      </c>
-      <c r="D207" t="s">
-        <v>17</v>
-      </c>
-      <c r="F207" s="6" t="s">
+      <c r="F214" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G214" s="6"/>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A215" t="s">
+        <v>609</v>
+      </c>
+      <c r="C215" t="s">
+        <v>610</v>
+      </c>
+      <c r="D215" t="s">
+        <v>71</v>
+      </c>
+      <c r="F215" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G215" s="6"/>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A216" t="s">
+        <v>611</v>
+      </c>
+      <c r="C216" t="s">
+        <v>612</v>
+      </c>
+      <c r="D216" t="s">
+        <v>9</v>
+      </c>
+      <c r="F216" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G216" s="6"/>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A217" t="s">
+        <v>613</v>
+      </c>
+      <c r="C217" t="s">
+        <v>614</v>
+      </c>
+      <c r="D217" t="s">
+        <v>615</v>
+      </c>
+      <c r="F217" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G217" s="6"/>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A218" t="s">
+        <v>616</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="D218" t="s">
+        <v>166</v>
+      </c>
+      <c r="F218" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G207" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A208" t="s">
-        <v>601</v>
-      </c>
-      <c r="C208" t="s">
-        <v>602</v>
-      </c>
-      <c r="D208" t="s">
-        <v>73</v>
-      </c>
-      <c r="F208" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G208" s="6"/>
-    </row>
-    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A209" t="s">
-        <v>603</v>
-      </c>
-      <c r="C209" t="s">
-        <v>604</v>
-      </c>
-      <c r="D209" t="s">
-        <v>135</v>
-      </c>
-      <c r="F209" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G209" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A210" t="s">
-        <v>605</v>
-      </c>
-      <c r="C210" t="s">
-        <v>606</v>
-      </c>
-      <c r="D210" t="s">
-        <v>168</v>
-      </c>
-      <c r="F210" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G210" s="6"/>
-    </row>
-    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A211" t="s">
-        <v>607</v>
-      </c>
-      <c r="C211" t="s">
-        <v>608</v>
-      </c>
-      <c r="D211" t="s">
-        <v>609</v>
-      </c>
-      <c r="F211" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G211" s="6"/>
-    </row>
-    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A212" t="s">
-        <v>610</v>
-      </c>
-      <c r="C212" t="s">
-        <v>611</v>
-      </c>
-      <c r="D212" t="s">
-        <v>168</v>
-      </c>
-      <c r="F212" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G212" s="6"/>
-    </row>
-    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A213" t="s">
-        <v>612</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="D213" t="s">
-        <v>614</v>
-      </c>
-      <c r="F213" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G213" s="6"/>
-    </row>
-    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A214" t="s">
-        <v>615</v>
-      </c>
-      <c r="C214" t="s">
-        <v>616</v>
-      </c>
-      <c r="D214" t="s">
-        <v>55</v>
-      </c>
-      <c r="F214" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G214" s="6"/>
-    </row>
-    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A215" t="s">
-        <v>617</v>
-      </c>
-      <c r="C215" t="s">
-        <v>618</v>
-      </c>
-      <c r="D215" t="s">
-        <v>9</v>
-      </c>
-      <c r="F215" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G215" s="6"/>
-    </row>
-    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A216" t="s">
-        <v>619</v>
-      </c>
-      <c r="C216" t="s">
-        <v>620</v>
-      </c>
-      <c r="D216" t="s">
-        <v>73</v>
-      </c>
-      <c r="F216" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G216" s="6"/>
-    </row>
-    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A217" t="s">
-        <v>621</v>
-      </c>
-      <c r="C217" t="s">
-        <v>622</v>
-      </c>
-      <c r="D217" t="s">
-        <v>9</v>
-      </c>
-      <c r="F217" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G217" s="6"/>
-    </row>
-    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A218" t="s">
-        <v>623</v>
-      </c>
-      <c r="C218" t="s">
-        <v>624</v>
-      </c>
-      <c r="D218" t="s">
-        <v>625</v>
-      </c>
-      <c r="F218" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G218" s="6"/>
+      <c r="G218" s="6" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>626</v>
-      </c>
-      <c r="C219" t="s">
-        <v>627</v>
+        <v>618</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>619</v>
       </c>
       <c r="D219" t="s">
-        <v>168</v>
-      </c>
-      <c r="F219" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G219" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+        <v>166</v>
+      </c>
+      <c r="F219" s="6"/>
+      <c r="G219" s="6"/>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>628</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>629</v>
+        <v>620</v>
+      </c>
+      <c r="C220" t="s">
+        <v>621</v>
       </c>
       <c r="D220" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F220" s="6" t="s">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="G220" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A221" t="s">
-        <v>630</v>
-      </c>
-      <c r="C221" t="s">
-        <v>631</v>
-      </c>
-      <c r="D221" t="s">
-        <v>168</v>
-      </c>
-      <c r="F221" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G221" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G221" xr:uid="{00000000-0009-0000-0000-000000000000}">
+  <autoFilter ref="A1:G113" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
-      <filters blank="1">
-        <filter val="ABB"/>
-        <filter val="Abbott"/>
-        <filter val="ABL Group"/>
-        <filter val="ABS"/>
-        <filter val="Aibel"/>
-        <filter val="AKZO NOBEL PAINTS (SINGAPORE) PTE. LTD."/>
-        <filter val="Baker Hughes"/>
-        <filter val="BASF"/>
-        <filter val="Baxter"/>
-        <filter val="BERGER PAINTS SINGAPORE PTE LTD"/>
-        <filter val="Bertschi"/>
-        <filter val="Black &amp; Veatch"/>
-        <filter val="BMT"/>
-        <filter val="BP"/>
-        <filter val="Bumi Armada"/>
-        <filter val="Bureau Veritas Marine &amp; Offshore"/>
-        <filter val="BW Offshore"/>
-        <filter val="Cameron (SLB)"/>
-        <filter val="ECOLAB PTE. LTD."/>
-        <filter val="EXXONMOBIL ASIA PACIFIC PTE. LTD."/>
-        <filter val="Global Maritime"/>
-        <filter val="GlobalFoundries"/>
-        <filter val="HBA Offshore"/>
-        <filter val="Jacobs"/>
-        <filter val="KBR"/>
-        <filter val="Kongsberg Maritime"/>
-        <filter val="KSB"/>
-        <filter val="Mitsubishi Chemical"/>
-        <filter val="MITSUBISHI CHEMICAL METHACRYLATES SINGAPORE PTE. LTD."/>
-        <filter val="Mitsubishi Electric"/>
-        <filter val="NOVABAY PTE. LTD."/>
-        <filter val="SABIC"/>
-        <filter val="SBM Offshore"/>
-        <filter val="Surbana Jurong"/>
-        <filter val="TRELLEBORG SINGAPORE PTE. LTD."/>
-        <filter val="WuXi Biologics"/>
+      <filters>
+        <filter val="PPG INDUSTRIES (SINGAPORE) PTE. LTD."/>
       </filters>
     </filterColumn>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="C175" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C205" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="C213" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="C220" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="C141" r:id="rId5" xr:uid="{C2B305E5-3E1F-EC42-A39C-9BCB261CC393}"/>
+    <hyperlink ref="C174" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C204" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="C212" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="C219" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="C140" r:id="rId5" xr:uid="{C2B305E5-3E1F-EC42-A39C-9BCB261CC393}"/>
     <hyperlink ref="C6" r:id="rId6" xr:uid="{FEB0E9A9-8BE3-3D45-BDD6-80B0DB982363}"/>
+    <hyperlink ref="C209" r:id="rId7" xr:uid="{4E73DFF4-D9A4-5A4C-B662-034068940838}"/>
+    <hyperlink ref="C195" r:id="rId8" xr:uid="{A885E56C-58F0-2340-8EFF-BC0DDC98FD35}"/>
+    <hyperlink ref="C54" r:id="rId9" xr:uid="{65FD9248-6593-7340-8E99-70D83A0BDC0A}"/>
+    <hyperlink ref="C211" r:id="rId10" xr:uid="{86951D57-E9F7-0748-B05B-BDA9DDD2F952}"/>
+    <hyperlink ref="C218" r:id="rId11" xr:uid="{756CBA95-0C00-FC4F-BB97-C8F7DE6F7A86}"/>
+    <hyperlink ref="C7" r:id="rId12" xr:uid="{881B0FEB-2F14-6840-A8C8-1C92F83887E2}"/>
+    <hyperlink ref="C55" r:id="rId13" display="https://careers.ppg.com/us/en/search-results?m=3&amp;location=Singapore%2C%20North%20East%2C%20Singapore" xr:uid="{948C709D-E26C-6B47-AF08-DB3D9D0B7ACF}"/>
+    <hyperlink ref="B79" r:id="rId14" xr:uid="{0102135B-8EA0-B04C-96D2-5C35A558E601}"/>
+    <hyperlink ref="C79" r:id="rId15" xr:uid="{664F1B2F-018B-F840-AF0A-CA31BD6351AA}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -6299,28 +6245,28 @@
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>10</v>
@@ -6329,45 +6275,45 @@
     </row>
     <row r="3" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>641</v>
+        <v>631</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G3" s="6"/>
     </row>
     <row r="4" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>14</v>

--- a/data/input/master-input_companies.xlsx
+++ b/data/input/master-input_companies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alirizabagci/Documents/04_Projekte_Code/Python Projects/Upwork/singapore_ats_scraping/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF5BDF42-A343-8C45-A4B5-279E676E14AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9158D043-D927-614B-B3E8-440B4BDEDF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">BP </t>
   </si>
   <si>
-    <t>careers.ppg.com/us/en/search-results?m=3&amp;location=Singapore%2C%20North%20East</t>
+    <t>https://careers.ppg.com/us/en/search-results?m=3&amp;location=Singapore%2C%20North%20East</t>
   </si>
 </sst>
 </file>
@@ -6225,7 +6225,7 @@
     <hyperlink ref="C211" r:id="rId10" xr:uid="{86951D57-E9F7-0748-B05B-BDA9DDD2F952}"/>
     <hyperlink ref="C218" r:id="rId11" xr:uid="{756CBA95-0C00-FC4F-BB97-C8F7DE6F7A86}"/>
     <hyperlink ref="C7" r:id="rId12" xr:uid="{881B0FEB-2F14-6840-A8C8-1C92F83887E2}"/>
-    <hyperlink ref="C55" r:id="rId13" display="https://careers.ppg.com/us/en/search-results?m=3&amp;location=Singapore%2C%20North%20East%2C%20Singapore" xr:uid="{948C709D-E26C-6B47-AF08-DB3D9D0B7ACF}"/>
+    <hyperlink ref="C55" r:id="rId13" xr:uid="{948C709D-E26C-6B47-AF08-DB3D9D0B7ACF}"/>
     <hyperlink ref="B79" r:id="rId14" xr:uid="{0102135B-8EA0-B04C-96D2-5C35A558E601}"/>
     <hyperlink ref="C79" r:id="rId15" xr:uid="{664F1B2F-018B-F840-AF0A-CA31BD6351AA}"/>
   </hyperlinks>
